--- a/media/formatos_excel/BITACORA_GESTION_PROYECTOS.xlsx
+++ b/media/formatos_excel/BITACORA_GESTION_PROYECTOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEONARD\python-dev\aplicaciones_incasur\media\formatos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B7EC566-0631-4348-A924-BDFED584FB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAEDEB0-708C-4DFA-B2C6-9EE3C54F69C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{66EB0D1F-43D8-4300-9F1D-D15AE56C93BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66EB0D1F-43D8-4300-9F1D-D15AE56C93BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +83,13 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,34 +116,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,157 +463,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F75167-B161-445D-A589-C52E83D450AA}">
   <dimension ref="B2:H42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -612,248 +622,248 @@
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="35" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B36:H42"/>
-    <mergeCell ref="B18:H33"/>
-    <mergeCell ref="B12:H15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:H5"/>
+    <mergeCell ref="B19:H33"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="D8:H9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B36:H42"/>
+    <mergeCell ref="B13:H16"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B35:D35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
